--- a/XlsxSharp.Tests/Resource/Examples/PivotTables/PivotTables.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/PivotTables/PivotTables.xlsx
@@ -1,82 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="PastrySalesData" sheetId="1" r:id="rId2"/>
-    <x:sheet name="pvt1" sheetId="2" r:id="rId3"/>
-    <x:sheet name="pvt2" sheetId="3" r:id="rId4"/>
-    <x:sheet name="pvt3" sheetId="4" r:id="rId5"/>
-    <x:sheet name="pvtNoColumnLabels" sheetId="5" r:id="rId6"/>
-    <x:sheet name="pvtCollapsedFields" sheetId="6" r:id="rId7"/>
-    <x:sheet name="pvtFieldAsValueAndLabel" sheetId="7" r:id="rId8"/>
-    <x:sheet name="pvtHideSubTotals" sheetId="8" r:id="rId9"/>
-    <x:sheet name="pvtFilter" sheetId="9" r:id="rId10"/>
-    <x:sheet name="pvtSort" sheetId="10" r:id="rId11"/>
-    <x:sheet name="pvtInteger" sheetId="11" r:id="rId12"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-  <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="rId15"/>
-  </x:pivotCaches>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="PastrySalesData" sheetId="1"/>
+    <sheet r:id="rId2" name="pvt1" sheetId="2"/>
+    <sheet r:id="rId3" name="pvt2" sheetId="3"/>
+    <sheet r:id="rId4" name="pvt3" sheetId="4"/>
+    <sheet r:id="rId5" name="pvtNoColumnLabels" sheetId="5"/>
+    <sheet r:id="rId6" name="pvtCollapsedFields" sheetId="6"/>
+    <sheet r:id="rId7" name="pvtFieldAsValueAndLabel" sheetId="7"/>
+    <sheet r:id="rId8" name="pvtHideSubTotals" sheetId="8"/>
+    <sheet r:id="rId9" name="pvtFilter" sheetId="9"/>
+    <sheet r:id="rId10" name="pvtSort" sheetId="10"/>
+    <sheet r:id="rId11" name="pvtInteger" sheetId="11"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId14"/>
+  </pivotCaches>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NumberOfOrders</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quality</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Month</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BakeDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Croissant</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>May</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Doughnut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bearclaw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Danish</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SconE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCONE</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>NumberOfOrders</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>BakeDate</t>
+  </si>
+  <si>
+    <t>Croissant</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Doughnut</t>
+  </si>
+  <si>
+    <t>Bearclaw</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>Scone</t>
+  </si>
+  <si>
+    <t>SconE</t>
+  </si>
+  <si>
+    <t>SCONE</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -129,7 +129,235 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" saveData="1" refreshOnLoad="1">
+  <cacheSource type="worksheet">
+    <worksheetSource name="PastrySalesData"/>
+  </cacheSource>
+  <cacheFields>
+    <cacheField name="Name">
+      <sharedItems count="5">
+        <s v="Croissant"/>
+        <s v="Doughnut"/>
+        <s v="Bearclaw"/>
+        <s v="Danish"/>
+        <s v="Scone"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Code">
+      <sharedItems count="6" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101" maxValue="105" containsString="0">
+        <n v="101"/>
+        <n v="102"/>
+        <n v="103"/>
+        <n v="104"/>
+        <n v="105"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="NumberOfOrders">
+      <sharedItems count="14" containsNumber="1" containsInteger="1" minValue="122" maxValue="394" containsSemiMixedTypes="0" containsString="0">
+        <n v="150"/>
+        <n v="250"/>
+        <n v="134"/>
+        <n v="225"/>
+        <n v="210"/>
+        <n v="184"/>
+        <n v="124"/>
+        <n v="394"/>
+        <n v="190"/>
+        <n v="221"/>
+        <n v="135"/>
+        <n v="122"/>
+        <n v="243"/>
+        <n v="255"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quality">
+      <sharedItems count="16" containsNumber="1" minValue="-20.24" maxValue="89.99" containsSemiMixedTypes="0" containsString="0">
+        <n v="60.2"/>
+        <n v="50.42"/>
+        <n v="22.12"/>
+        <n v="89.99"/>
+        <n v="70"/>
+        <n v="75.33"/>
+        <n v="10.24"/>
+        <n v="33.33"/>
+        <n v="25"/>
+        <n v="-20.24"/>
+        <n v="60"/>
+        <n v="24.76"/>
+        <n v="0"/>
+        <n v="5.19"/>
+        <n v="44.2"/>
+        <n v="18.4"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Month">
+      <sharedItems count="4" containsBlank="1">
+        <s v="Apr"/>
+        <s v="May"/>
+        <s v="Jun"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="BakeDate">
+      <sharedItems count="16" containsBlank="1" containsDate="1" containsNonDate="0" minDate="2016-04-21T00:00:00" maxDate="2017-06-14T00:00:00" containsString="0">
+        <d v="2016-04-21T00:00:00"/>
+        <d v="2016-05-03T00:00:00"/>
+        <d v="2016-06-24T00:00:00"/>
+        <d v="2017-04-23T00:00:00"/>
+        <d v="2016-05-24T00:00:00"/>
+        <d v="2016-06-02T00:00:00"/>
+        <d v="2016-04-27T00:00:00"/>
+        <d v="2016-05-20T00:00:00"/>
+        <d v="2017-06-05T00:00:00"/>
+        <d v="2017-04-24T00:00:00"/>
+        <d v="2017-05-08T00:00:00"/>
+        <d v="2016-06-21T00:00:00"/>
+        <d v="2017-04-22T00:00:00"/>
+        <d v="2017-05-03T00:00:00"/>
+        <d v="2017-06-14T00:00:00"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="Croissant"/>
+    <n v="101"/>
+    <n v="150"/>
+    <n v="60.2"/>
+    <s v="Apr"/>
+    <d v="2016-04-21T00:00:00"/>
+  </r>
+  <r>
+    <s v="Croissant"/>
+    <n v="101"/>
+    <n v="250"/>
+    <n v="50.42"/>
+    <s v="May"/>
+    <d v="2016-05-03T00:00:00"/>
+  </r>
+  <r>
+    <s v="Croissant"/>
+    <n v="101"/>
+    <n v="134"/>
+    <n v="22.12"/>
+    <s v="Jun"/>
+    <d v="2016-06-24T00:00:00"/>
+  </r>
+  <r>
+    <s v="Doughnut"/>
+    <n v="102"/>
+    <n v="250"/>
+    <n v="89.99"/>
+    <s v="Apr"/>
+    <d v="2017-04-23T00:00:00"/>
+  </r>
+  <r>
+    <s v="Doughnut"/>
+    <n v="102"/>
+    <n v="225"/>
+    <n v="70"/>
+    <s v="May"/>
+    <d v="2016-05-24T00:00:00"/>
+  </r>
+  <r>
+    <s v="Doughnut"/>
+    <n v="102"/>
+    <n v="210"/>
+    <n v="75.33"/>
+    <s v="Jun"/>
+    <d v="2016-06-02T00:00:00"/>
+  </r>
+  <r>
+    <s v="Bearclaw"/>
+    <n v="103"/>
+    <n v="134"/>
+    <n v="10.24"/>
+    <s v="Apr"/>
+    <d v="2016-04-27T00:00:00"/>
+  </r>
+  <r>
+    <s v="Bearclaw"/>
+    <n v="103"/>
+    <n v="184"/>
+    <n v="33.33"/>
+    <s v="May"/>
+    <d v="2016-05-20T00:00:00"/>
+  </r>
+  <r>
+    <s v="Bearclaw"/>
+    <n v="103"/>
+    <n v="124"/>
+    <n v="25"/>
+    <s v="Jun"/>
+    <d v="2017-06-05T00:00:00"/>
+  </r>
+  <r>
+    <s v="Danish"/>
+    <n v="104"/>
+    <n v="394"/>
+    <n v="-20.24"/>
+    <s v="Apr"/>
+    <d v="2017-04-24T00:00:00"/>
+  </r>
+  <r>
+    <s v="Danish"/>
+    <n v="104"/>
+    <n v="190"/>
+    <n v="60"/>
+    <s v="May"/>
+    <d v="2017-05-08T00:00:00"/>
+  </r>
+  <r>
+    <s v="Danish"/>
+    <n v="104"/>
+    <n v="221"/>
+    <n v="24.76"/>
+    <s v="Jun"/>
+    <d v="2016-06-21T00:00:00"/>
+  </r>
+  <r>
+    <s v="Scone"/>
+    <n v="105"/>
+    <n v="135"/>
+    <n v="0"/>
+    <s v="Apr"/>
+    <d v="2017-04-22T00:00:00"/>
+  </r>
+  <r>
+    <s v="SconE"/>
+    <n v="105"/>
+    <n v="122"/>
+    <n v="5.19"/>
+    <s v="May"/>
+    <d v="2017-05-03T00:00:00"/>
+  </r>
+  <r>
+    <s v="SCONE"/>
+    <n v="105"/>
+    <n v="243"/>
+    <n v="44.2"/>
+    <s v="Jun"/>
+    <d v="2017-06-14T00:00:00"/>
+  </r>
+  <r>
+    <s v="Scone"/>
+    <m/>
+    <n v="255"/>
+    <n v="18.4"/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
@@ -656,18 +884,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PastrySalesData" displayName="PastrySalesData" ref="A1:F17" totalsRowShown="0">
-  <x:autoFilter ref="A1:F17"/>
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="Name"/>
-    <x:tableColumn id="2" name="Code"/>
-    <x:tableColumn id="3" name="NumberOfOrders"/>
-    <x:tableColumn id="4" name="Quality"/>
-    <x:tableColumn id="5" name="Month"/>
-    <x:tableColumn id="6" name="BakeDate"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PastrySalesData" displayName="PastrySalesData" ref="A1:F17" totalsRowShown="0">
+  <autoFilter ref="A1:F17"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Name"/>
+    <tableColumn id="2" name="Code"/>
+    <tableColumn id="3" name="NumberOfOrders"/>
+    <tableColumn id="4" name="Quality"/>
+    <tableColumn id="5" name="Month"/>
+    <tableColumn id="6" name="BakeDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -954,747 +1182,519 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:F17"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.710625" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:6">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D2" s="0">
-        <x:v>60.2</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="1">
-        <x:v>42481</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D3" s="0">
-        <x:v>50.42</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F3" s="1">
-        <x:v>42493</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
-        <x:v>22.12</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F4" s="1">
-        <x:v>42545</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>89.99</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F5" s="1">
-        <x:v>42848</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F6" s="1">
-        <x:v>42514</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D7" s="0">
-        <x:v>75.33</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F7" s="1">
-        <x:v>42523</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D8" s="0">
-        <x:v>10.24</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F8" s="1">
-        <x:v>42487</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6">
-      <x:c r="A9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D9" s="0">
-        <x:v>33.33</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F9" s="1">
-        <x:v>42510</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
-      <x:c r="A10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D10" s="0">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F10" s="1">
-        <x:v>42891</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6">
-      <x:c r="A11" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B11" s="0">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="D11" s="0">
-        <x:v>-20.24</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F11" s="1">
-        <x:v>42849</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:6">
-      <x:c r="A12" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D12" s="0">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F12" s="1">
-        <x:v>42863</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:6">
-      <x:c r="A13" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="0">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D13" s="0">
-        <x:v>24.76</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F13" s="1">
-        <x:v>42542</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:6">
-      <x:c r="A14" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B14" s="0">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F14" s="1">
-        <x:v>42847</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:6">
-      <x:c r="A15" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B15" s="0">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D15" s="0">
-        <x:v>5.19</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F15" s="1">
-        <x:v>42858</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:6">
-      <x:c r="A16" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B16" s="0">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D16" s="0">
-        <x:v>44.2</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F16" s="1">
-        <x:v>42900</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6">
-      <x:c r="A17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D17" s="0">
-        <x:v>18.4</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="1">
-    <x:tablePart r:id="rId16"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="9.996339"/>
+    <col min="2" max="2" style="0" customWidth="1" width="7.710625"/>
+    <col min="3" max="3" style="0" customWidth="1" width="18.710625"/>
+    <col min="4" max="4" style="0" customWidth="1" width="9.710625"/>
+    <col min="5" max="5" style="0" customWidth="1" width="9.567768"/>
+    <col min="6" max="6" style="0" customWidth="1" width="11.710625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="0">
+        <v>101</v>
+      </c>
+      <c r="C2" s="0">
+        <v>150</v>
+      </c>
+      <c r="D2" s="0">
+        <v>60.2</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1">
+        <v>42481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="0">
+        <v>101</v>
+      </c>
+      <c r="C3" s="0">
+        <v>250</v>
+      </c>
+      <c r="D3" s="0">
+        <v>50.42</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1">
+        <v>42493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0">
+        <v>101</v>
+      </c>
+      <c r="C4" s="0">
+        <v>134</v>
+      </c>
+      <c r="D4" s="0">
+        <v>22.12</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1">
+        <v>42545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="0">
+        <v>102</v>
+      </c>
+      <c r="C5" s="0">
+        <v>250</v>
+      </c>
+      <c r="D5" s="0">
+        <v>89.99</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1">
+        <v>42848</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="0">
+        <v>102</v>
+      </c>
+      <c r="C6" s="0">
+        <v>225</v>
+      </c>
+      <c r="D6" s="0">
+        <v>70</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1">
+        <v>42514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="0">
+        <v>102</v>
+      </c>
+      <c r="C7" s="0">
+        <v>210</v>
+      </c>
+      <c r="D7" s="0">
+        <v>75.33</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1">
+        <v>42523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="0">
+        <v>103</v>
+      </c>
+      <c r="C8" s="0">
+        <v>134</v>
+      </c>
+      <c r="D8" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>42487</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="0">
+        <v>103</v>
+      </c>
+      <c r="C9" s="0">
+        <v>184</v>
+      </c>
+      <c r="D9" s="0">
+        <v>33.33</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>42510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="0">
+        <v>103</v>
+      </c>
+      <c r="C10" s="0">
+        <v>124</v>
+      </c>
+      <c r="D10" s="0">
+        <v>25</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1">
+        <v>42891</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="0">
+        <v>104</v>
+      </c>
+      <c r="C11" s="0">
+        <v>394</v>
+      </c>
+      <c r="D11" s="0">
+        <v>-20.24</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1">
+        <v>42849</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="0">
+        <v>104</v>
+      </c>
+      <c r="C12" s="0">
+        <v>190</v>
+      </c>
+      <c r="D12" s="0">
+        <v>60</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>42863</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>104</v>
+      </c>
+      <c r="C13" s="0">
+        <v>221</v>
+      </c>
+      <c r="D13" s="0">
+        <v>24.76</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1">
+        <v>42542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>105</v>
+      </c>
+      <c r="C14" s="0">
+        <v>135</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="1">
+        <v>42847</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>105</v>
+      </c>
+      <c r="C15" s="0">
+        <v>122</v>
+      </c>
+      <c r="D15" s="0">
+        <v>5.19</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>42858</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>105</v>
+      </c>
+      <c r="C16" s="0">
+        <v>243</v>
+      </c>
+      <c r="D16" s="0">
+        <v>44.2</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="0">
+        <v>255</v>
+      </c>
+      <c r="D17" s="0">
+        <v>18.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId15"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource name="PastrySalesData"/>
-  </x:cacheSource>
-  <x:cacheFields>
-    <x:cacheField name="Name">
-      <x:sharedItems count="5">
-        <x:s v="Croissant"/>
-        <x:s v="Doughnut"/>
-        <x:s v="Bearclaw"/>
-        <x:s v="Danish"/>
-        <x:s v="Scone"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Code">
-      <x:sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101" maxValue="105" count="6">
-        <x:n v="101"/>
-        <x:n v="102"/>
-        <x:n v="103"/>
-        <x:n v="104"/>
-        <x:n v="105"/>
-        <x:m/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="NumberOfOrders">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="122" maxValue="394" count="14">
-        <x:n v="150"/>
-        <x:n v="250"/>
-        <x:n v="134"/>
-        <x:n v="225"/>
-        <x:n v="210"/>
-        <x:n v="184"/>
-        <x:n v="124"/>
-        <x:n v="394"/>
-        <x:n v="190"/>
-        <x:n v="221"/>
-        <x:n v="135"/>
-        <x:n v="122"/>
-        <x:n v="243"/>
-        <x:n v="255"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quality">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-20.24" maxValue="89.99" count="16">
-        <x:n v="60.2"/>
-        <x:n v="50.42"/>
-        <x:n v="22.12"/>
-        <x:n v="89.99"/>
-        <x:n v="70"/>
-        <x:n v="75.33"/>
-        <x:n v="10.24"/>
-        <x:n v="33.33"/>
-        <x:n v="25"/>
-        <x:n v="-20.24"/>
-        <x:n v="60"/>
-        <x:n v="24.76"/>
-        <x:n v="0"/>
-        <x:n v="5.19"/>
-        <x:n v="44.2"/>
-        <x:n v="18.4"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Month">
-      <x:sharedItems containsBlank="1" count="4">
-        <x:s v="Apr"/>
-        <x:s v="May"/>
-        <x:s v="Jun"/>
-        <x:m/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="BakeDate">
-      <x:sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2016-04-21T00:00:00" maxDate="2017-06-14T00:00:00" count="16">
-        <x:d v="2016-04-21T00:00:00"/>
-        <x:d v="2016-05-03T00:00:00"/>
-        <x:d v="2016-06-24T00:00:00"/>
-        <x:d v="2017-04-23T00:00:00"/>
-        <x:d v="2016-05-24T00:00:00"/>
-        <x:d v="2016-06-02T00:00:00"/>
-        <x:d v="2016-04-27T00:00:00"/>
-        <x:d v="2016-05-20T00:00:00"/>
-        <x:d v="2017-06-05T00:00:00"/>
-        <x:d v="2017-04-24T00:00:00"/>
-        <x:d v="2017-05-08T00:00:00"/>
-        <x:d v="2016-06-21T00:00:00"/>
-        <x:d v="2017-04-22T00:00:00"/>
-        <x:d v="2017-05-03T00:00:00"/>
-        <x:d v="2017-06-14T00:00:00"/>
-        <x:m/>
-      </x:sharedItems>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
-  <r>
-    <s v="Croissant"/>
-    <n v="101"/>
-    <n v="150"/>
-    <n v="60.2"/>
-    <s v="Apr"/>
-    <d v="2016-04-21T00:00:00"/>
-  </r>
-  <r>
-    <s v="Croissant"/>
-    <n v="101"/>
-    <n v="250"/>
-    <n v="50.42"/>
-    <s v="May"/>
-    <d v="2016-05-03T00:00:00"/>
-  </r>
-  <r>
-    <s v="Croissant"/>
-    <n v="101"/>
-    <n v="134"/>
-    <n v="22.12"/>
-    <s v="Jun"/>
-    <d v="2016-06-24T00:00:00"/>
-  </r>
-  <r>
-    <s v="Doughnut"/>
-    <n v="102"/>
-    <n v="250"/>
-    <n v="89.99"/>
-    <s v="Apr"/>
-    <d v="2017-04-23T00:00:00"/>
-  </r>
-  <r>
-    <s v="Doughnut"/>
-    <n v="102"/>
-    <n v="225"/>
-    <n v="70"/>
-    <s v="May"/>
-    <d v="2016-05-24T00:00:00"/>
-  </r>
-  <r>
-    <s v="Doughnut"/>
-    <n v="102"/>
-    <n v="210"/>
-    <n v="75.33"/>
-    <s v="Jun"/>
-    <d v="2016-06-02T00:00:00"/>
-  </r>
-  <r>
-    <s v="Bearclaw"/>
-    <n v="103"/>
-    <n v="134"/>
-    <n v="10.24"/>
-    <s v="Apr"/>
-    <d v="2016-04-27T00:00:00"/>
-  </r>
-  <r>
-    <s v="Bearclaw"/>
-    <n v="103"/>
-    <n v="184"/>
-    <n v="33.33"/>
-    <s v="May"/>
-    <d v="2016-05-20T00:00:00"/>
-  </r>
-  <r>
-    <s v="Bearclaw"/>
-    <n v="103"/>
-    <n v="124"/>
-    <n v="25"/>
-    <s v="Jun"/>
-    <d v="2017-06-05T00:00:00"/>
-  </r>
-  <r>
-    <s v="Danish"/>
-    <n v="104"/>
-    <n v="394"/>
-    <n v="-20.24"/>
-    <s v="Apr"/>
-    <d v="2017-04-24T00:00:00"/>
-  </r>
-  <r>
-    <s v="Danish"/>
-    <n v="104"/>
-    <n v="190"/>
-    <n v="60"/>
-    <s v="May"/>
-    <d v="2017-05-08T00:00:00"/>
-  </r>
-  <r>
-    <s v="Danish"/>
-    <n v="104"/>
-    <n v="221"/>
-    <n v="24.76"/>
-    <s v="Jun"/>
-    <d v="2016-06-21T00:00:00"/>
-  </r>
-  <r>
-    <s v="Scone"/>
-    <n v="105"/>
-    <n v="135"/>
-    <n v="0"/>
-    <s v="Apr"/>
-    <d v="2017-04-22T00:00:00"/>
-  </r>
-  <r>
-    <s v="SconE"/>
-    <n v="105"/>
-    <n v="122"/>
-    <n v="5.19"/>
-    <s v="May"/>
-    <d v="2017-05-03T00:00:00"/>
-  </r>
-  <r>
-    <s v="SCONE"/>
-    <n v="105"/>
-    <n v="243"/>
-    <n v="44.2"/>
-    <s v="Jun"/>
-    <d v="2017-06-14T00:00:00"/>
-  </r>
-  <r>
-    <s v="Scone"/>
-    <m/>
-    <n v="255"/>
-    <n v="18.4"/>
-    <m/>
-    <m/>
-  </r>
-</pivotCacheRecords>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>